--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_036.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_036.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFAFA4D0-C811-4384-883A-B4CE09A2BABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC352839-50F6-4383-94A5-6E18EF9EACF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -642,13 +642,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S06aH03,S01aH03,S05aH03,S02aH03,S03aH03,S04aH03</t>
+    <t>S04aH03,S02aH03,S01aH03,S05aH03,S03aH03,S06aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S05aH04,S06aH02,S04aH05,S06aH01,S02aH02,S02aH04,S02aH05,S01aH02,S04aH04,S03aH01,S01aH04,S05aH01,S03aH02,S01aH05,S06aH05,S04aH02,S03aH05,S05aH05,S06aH04,S03aH04,S02aH01,S05aH02</t>
+    <t>S03aH04,S02aH01,S05aH02,S01aH02,S04aH04,S01aH01,S04aH01,S05aH04,S06aH02,S04aH02,S04aH05,S06aH01,S02aH04,S02aH05,S03aH01,S01aH05,S06aH05,S01aH04,S05aH01,S02aH02,S03aH02,S03aH05,S05aH05,S06aH04</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH01,S04aH01,S05aH04,S06aH02,S04aH05,S06aH01,S02aH02,S02aH04,S02aH05,S01aH02,S04aH04,S03aH01,S01aH04,S05aH01,S03aH02,S01aH05,S06aH05,S04aH02,S03aH05,S05aH05,S06aH04,S03aH04,S02aH01,S05aH02</v>
+        <v>S03aH04,S02aH01,S05aH02,S01aH02,S04aH04,S01aH01,S04aH01,S05aH04,S06aH02,S04aH02,S04aH05,S06aH01,S02aH04,S02aH05,S03aH01,S01aH05,S06aH05,S01aH04,S05aH01,S02aH02,S03aH02,S03aH05,S05aH05,S06aH04</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S06aH03,S01aH03,S05aH03,S02aH03,S03aH03,S04aH03</v>
+        <v>S04aH03,S02aH03,S01aH03,S05aH03,S03aH03,S06aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1371,7 +1371,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D5E6BF-A2F6-4B27-A4A6-17EDDC58E09E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66559AEA-0B90-48CF-9BC8-33B5AE213389}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1477,7 +1477,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44FF5CC0-DBD5-4B81-9701-83C173383F58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96553DC-B128-465F-8DCD-537A44C49D0D}">
   <dimension ref="B9:O610"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20739,7 +20739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9F66FA-242C-47B8-BC50-CDC5C3062B8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB1E4B1-B99B-4768-B0DA-781A9C21AE84}">
   <dimension ref="B9:EF60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31892,7 +31892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E586C5-4639-4661-BC9A-0D254463A22F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D778D648-DE5B-43FA-AD4E-3BBF18C6D128}">
   <dimension ref="B9:E40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32342,7 +32342,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1622F3-5928-4347-9CCB-63AB0616E2D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3707E1C1-5136-414D-9DAB-569368459041}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33029,7 +33029,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA123711-3AAE-4293-906C-B7B3C02E4877}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD1CB46-810A-472F-9D08-6458A3E141B5}">
   <dimension ref="B9:D40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33386,7 +33386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC46D798-4EA9-40DA-BD80-B85A5AF34323}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA8D07D-DD1D-4643-A9B8-81B4086DAA0D}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33460,7 +33460,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="E14" t="s">
         <v>208</v>
@@ -33614,7 +33614,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.16902857142857144</v>
+        <v>0.16902857142857139</v>
       </c>
       <c r="E25" t="s">
         <v>208</v>
@@ -33866,7 +33866,7 @@
         <v>43</v>
       </c>
       <c r="D43">
-        <v>0.23651428571428568</v>
+        <v>0.2365142857142857</v>
       </c>
       <c r="E43" t="s">
         <v>208</v>
@@ -34118,7 +34118,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.26065714285714281</v>
+        <v>0.26065714285714287</v>
       </c>
       <c r="E61" t="s">
         <v>208</v>
@@ -34216,7 +34216,7 @@
         <v>45</v>
       </c>
       <c r="D68">
-        <v>0.24779999999999999</v>
+        <v>0.24780000000000002</v>
       </c>
       <c r="E68" t="s">
         <v>208</v>
@@ -34300,7 +34300,7 @@
         <v>45</v>
       </c>
       <c r="D74">
-        <v>0.22766666666666668</v>
+        <v>0.22766666666666666</v>
       </c>
       <c r="E74" t="s">
         <v>208</v>
@@ -35126,7 +35126,7 @@
         <v>43</v>
       </c>
       <c r="D133">
-        <v>0.25260000000000005</v>
+        <v>0.25259999999999999</v>
       </c>
       <c r="E133" t="s">
         <v>208</v>
@@ -35140,7 +35140,7 @@
         <v>45</v>
       </c>
       <c r="D134">
-        <v>0.21929999999999997</v>
+        <v>0.21930000000000002</v>
       </c>
       <c r="E134" t="s">
         <v>208</v>
@@ -35294,7 +35294,7 @@
         <v>43</v>
       </c>
       <c r="D145">
-        <v>0.22011428571428571</v>
+        <v>0.22011428571428573</v>
       </c>
       <c r="E145" t="s">
         <v>208</v>
@@ -35378,7 +35378,7 @@
         <v>43</v>
       </c>
       <c r="D151">
-        <v>0.24881428571428571</v>
+        <v>0.24881428571428574</v>
       </c>
       <c r="E151" t="s">
         <v>208</v>
@@ -35546,7 +35546,7 @@
         <v>43</v>
       </c>
       <c r="D163">
-        <v>0.23360000000000003</v>
+        <v>0.2336</v>
       </c>
       <c r="E163" t="s">
         <v>208</v>
@@ -35630,7 +35630,7 @@
         <v>43</v>
       </c>
       <c r="D169">
-        <v>0.25347142857142857</v>
+        <v>0.25347142857142863</v>
       </c>
       <c r="E169" t="s">
         <v>208</v>
@@ -35728,7 +35728,7 @@
         <v>45</v>
       </c>
       <c r="D176">
-        <v>0.23019999999999999</v>
+        <v>0.23020000000000004</v>
       </c>
       <c r="E176" t="s">
         <v>208</v>
